--- a/naver-place-crawler/results_hair/동구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/동구_미용실.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -567,11 +567,7 @@
           <t>블루가이</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>red8276@naver.com</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
@@ -661,11 +657,7 @@
           <t>헤어코코</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>n_n_v_v@naver.com</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,11 +837,7 @@
           <t>그린헤어샵</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>yjd4843@naver.com</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
@@ -1029,11 +1017,7 @@
           <t>찌꼬뽀꼬</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ggiccoppocco@naver.com</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
@@ -1299,11 +1283,7 @@
           <t>그린미용실</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>govl733@naver.com</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
@@ -1659,11 +1639,7 @@
           <t>긋시아헤어 동인천역 본점</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>lovedarl2@naver.com</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
@@ -1937,11 +1913,7 @@
           <t>블루마린미용실</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>hairyuep@naver.com</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
@@ -2031,11 +2003,7 @@
           <t>디오헤어</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>dojin440@naver.com</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
@@ -2125,11 +2093,7 @@
           <t>송이미용실</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>alohasy0792@naver.com</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
@@ -2219,11 +2183,7 @@
           <t>카리스마</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>jackieyou@naver.com</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
@@ -2403,11 +2363,7 @@
           <t>준헤어아트</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>jie0105@naver.com</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
@@ -2669,11 +2625,7 @@
           <t>살롱드비아</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>tpfud1124@naver.com</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
@@ -2763,11 +2715,7 @@
           <t>정아미용실</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>bora4141@naver.com</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
@@ -2939,11 +2887,7 @@
           <t>보헤미안헤어</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>125_suu@naver.com</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
@@ -3397,11 +3341,7 @@
           <t>김영선헤어파라팜</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>hjstylemm@naver.com</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
@@ -3491,11 +3431,7 @@
           <t>한지수헤어스타</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>love444477@naver.com</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
@@ -3585,11 +3521,7 @@
           <t>달컴헤어</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>moonsb1206@naver.com</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
@@ -3679,11 +3611,7 @@
           <t>퀸헤어</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>ouou1771@naver.com</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
@@ -3859,11 +3787,7 @@
           <t>젠틀맨</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>dannykim2010@naver.com</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
@@ -4129,11 +4053,7 @@
           <t>은지헤어샵</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>south0429@naver.com</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
@@ -4223,11 +4143,7 @@
           <t>헤어5.5</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>tnrua34@naver.com</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
@@ -4317,11 +4233,7 @@
           <t>칼라헤어샵</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>color63676@naver.com</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
@@ -4501,11 +4413,7 @@
           <t>예쁜머리</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>propshop@naver.com</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
@@ -4681,11 +4589,7 @@
           <t>장헤어샵</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>jjongs10@naver.com</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
@@ -4861,11 +4765,7 @@
           <t>N.5 송현점</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>nabannnn@naver.com</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
@@ -5041,11 +4941,7 @@
           <t>올뎃헤어</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>gashwoon@naver.com</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
@@ -5135,11 +5031,7 @@
           <t>유나샵</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>yuna10110@naver.com</t>
-        </is>
-      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
@@ -5409,11 +5301,7 @@
           <t>홈헤어살롱</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>jiyea_junjin@naver.com</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
@@ -5499,11 +5387,7 @@
           <t>착한미용실</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>slayfox@naver.com</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
@@ -5675,11 +5559,7 @@
           <t>착한미용실</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>slayfox@naver.com</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
@@ -5863,11 +5743,7 @@
           <t>헤어박스</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>kpackage@naver.com</t>
-        </is>
-      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
@@ -6047,11 +5923,7 @@
           <t>아델라 헤어</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>hkhj8083@naver.com</t>
-        </is>
-      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
@@ -6141,11 +6013,7 @@
           <t>머리만들기</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>greencoy79@naver.com</t>
-        </is>
-      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
@@ -6235,11 +6103,7 @@
           <t>레지나헤어</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>zipyzigi2001@naver.com</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
@@ -6329,11 +6193,7 @@
           <t>미카엘헤어</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>lhw2611@naver.com</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
@@ -6423,11 +6283,7 @@
           <t>남자만들기</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>timmy0326@naver.com</t>
-        </is>
-      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
@@ -6517,11 +6373,7 @@
           <t>임진선헤어모드</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>hjstylemm@naver.com</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
@@ -6611,11 +6463,7 @@
           <t>진헤어</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>sspmj501@naver.com</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
@@ -6889,11 +6737,7 @@
           <t>아이원헤어</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>leeareum96@naver.com</t>
-        </is>
-      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
@@ -6983,11 +6827,7 @@
           <t>더끌림헤어</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>kklim7512820@naver.com</t>
-        </is>
-      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
@@ -7073,11 +6913,7 @@
           <t>젠틀맨</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>dannykim2010@naver.com</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
@@ -7253,11 +7089,7 @@
           <t>현대이발관</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>sacheoncity@naver.com</t>
-        </is>
-      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
@@ -7343,11 +7175,7 @@
           <t>시대이발관</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>ic-museum@naver.com</t>
-        </is>
-      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_hair/동구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/동구_미용실.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -567,7 +567,11 @@
           <t>블루가이</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>duswls1338@naver.com</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
@@ -642,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -657,7 +661,11 @@
           <t>헤어코코</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>n_n_v_v@naver.com</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
@@ -732,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -747,7 +755,11 @@
           <t>헤어블리스</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mini2028@naver.com</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
@@ -822,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -837,7 +849,11 @@
           <t>그린헤어샵</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>yjd4843@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
@@ -912,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -927,7 +943,11 @@
           <t>웨이비헤어</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>banana2728@naver.com</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
@@ -1002,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1037,11 @@
           <t>찌꼬뽀꼬</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ggiccoppocco@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
@@ -1092,7 +1116,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1131,11 @@
           <t>신데렐라헤어살롱</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>wonjung8542@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
@@ -1182,7 +1210,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1225,11 @@
           <t>다가즈 헤어 동인천점</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>tmxkdlf70@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -1243,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q9" t="n">
         <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1268,7 +1300,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1315,11 @@
           <t>그린미용실</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>govl733@naver.com</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
@@ -1358,7 +1394,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1409,11 @@
           <t>고은헤어</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>goodkej104@naver.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -1444,7 +1484,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1499,11 @@
           <t>오르세헤어</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>dhgngkstlek@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
@@ -1534,7 +1578,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1593,11 @@
           <t>헤어 림</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>amurug1_nuna@naver.com</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
@@ -1624,7 +1672,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1687,11 @@
           <t>긋시아헤어 동인천역 본점</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>lovedarl2@naver.com</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
@@ -1714,7 +1766,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1860,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1875,11 @@
           <t>요미살롱</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>minji_3-@naver.com</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
@@ -1898,7 +1954,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1969,11 @@
           <t>블루마린미용실</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>hairyuep@naver.com</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
@@ -1988,7 +2048,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2063,11 @@
           <t>디오헤어</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>dojin440@naver.com</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
@@ -2078,7 +2142,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2157,11 @@
           <t>송이미용실</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>alohasy0792@naver.com</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
@@ -2168,7 +2236,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2251,11 @@
           <t>카리스마</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jackieyou@naver.com</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
@@ -2258,7 +2330,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2345,11 @@
           <t>나타나엘헤어</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>yuujiin@naver.com</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
@@ -2348,7 +2424,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2439,11 @@
           <t>준헤어아트</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jie0105@naver.com</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
@@ -2434,7 +2514,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2529,11 @@
           <t>에스제이헤어</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>emkim1003@naver.com</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
@@ -2520,7 +2604,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2619,11 @@
           <t>어나더스타일</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>jadenchoe@naver.com</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
@@ -2610,7 +2698,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2788,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2803,11 @@
           <t>정아미용실</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>bora4141@naver.com</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
@@ -2786,7 +2878,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2893,11 @@
           <t>태쁘헤어</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>tjdwlsl2004@naver.com</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
@@ -2872,7 +2968,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2983,11 @@
           <t>보헤미안헤어</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>125_suu@naver.com</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
@@ -2962,7 +3062,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2977,7 +3077,11 @@
           <t>양지헤어모디컬 송림1호점</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>justdoit0706@naver.com</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
@@ -3052,7 +3156,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3171,11 @@
           <t>조이헤어샵</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>wedbl@naver.com</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
@@ -3142,7 +3250,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3265,11 @@
           <t>솔빛헤어샾</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>lovesmoothz@naver.com</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
@@ -3232,7 +3344,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3438,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3453,11 @@
           <t>김영선헤어파라팜</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>hjstylemm@naver.com</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
@@ -3416,7 +3532,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3622,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3637,11 @@
           <t>달컴헤어</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>moonsb1206@naver.com</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
@@ -3596,7 +3716,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3731,11 @@
           <t>퀸헤어</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ouou1771@naver.com</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
@@ -3682,7 +3806,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3821,11 @@
           <t>아가페헤어모드</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>hiksanin@naver.com</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
@@ -3772,7 +3900,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3915,11 @@
           <t>젠틀맨</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>dannykim2010@naver.com</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
@@ -3862,7 +3994,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3877,7 +4009,11 @@
           <t>루나헤어</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>hott0116@naver.com</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
@@ -3948,7 +4084,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3963,7 +4099,11 @@
           <t>앨리스헤어</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>oh-hair@naver.com</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
@@ -4038,7 +4178,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4268,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4283,11 @@
           <t>헤어5.5</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>tnrua34@naver.com</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
@@ -4218,7 +4362,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4377,11 @@
           <t>칼라헤어샵</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>color63676@naver.com</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
@@ -4308,7 +4456,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4471,11 @@
           <t>오늘은머리하는날</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>uiryeonginfo@naver.com</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
@@ -4398,7 +4550,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4565,11 @@
           <t>예쁜머리</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>propshop@naver.com</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
@@ -4484,7 +4640,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4655,11 @@
           <t>그녀는예뻤다헤어샵</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>curablee@naver.com</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
@@ -4574,7 +4734,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4749,11 @@
           <t>장헤어샵</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>jjongs10@naver.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
@@ -4660,7 +4824,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4839,11 @@
           <t>모퉁이미장원</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>nijal99@naver.com</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
@@ -4750,7 +4918,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4933,11 @@
           <t>N.5 송현점</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>nabannnn@naver.com</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
@@ -4836,7 +5008,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4851,7 +5023,11 @@
           <t>챠밍헤어클럽</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>dongsimgi1004@naver.com</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
@@ -4926,7 +5102,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4941,7 +5117,11 @@
           <t>올뎃헤어</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>gashwoon@naver.com</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
@@ -5016,7 +5196,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5211,11 @@
           <t>유나샵</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>yuna10110@naver.com</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
@@ -5106,7 +5290,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5305,11 @@
           <t>은헤어샵</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>dla_dp_fls@naver.com</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
@@ -5196,7 +5384,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5399,11 @@
           <t>장미미용실</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>shanyingstar@naver.com</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
@@ -5286,7 +5478,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5493,11 @@
           <t>홈헤어살롱</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>jiyea_junjin@naver.com</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
@@ -5372,7 +5568,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5387,7 +5583,11 @@
           <t>착한미용실</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>slayfox@naver.com</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
@@ -5458,7 +5658,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5744,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5759,11 @@
           <t>착한미용실</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>slayfox@naver.com</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
@@ -5634,7 +5838,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5932,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5947,11 @@
           <t>헤어박스</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>kpackage@naver.com</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
@@ -5818,7 +6026,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5833,7 +6041,11 @@
           <t>초이스헤어</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>nrzzzzzz@naver.com</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
@@ -5908,7 +6120,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5998,7 +6210,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6300,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6315,11 @@
           <t>레지나헤어</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>zipyzigi2001@naver.com</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
@@ -6178,7 +6394,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6409,11 @@
           <t>미카엘헤어</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>lhw2611@naver.com</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
@@ -6268,7 +6488,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6503,11 @@
           <t>남자만들기</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>timmy0326@naver.com</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
@@ -6358,7 +6582,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6597,11 @@
           <t>임진선헤어모드</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>hjstylemm@naver.com</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
@@ -6448,7 +6676,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6691,11 @@
           <t>진헤어</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>sspmj501@naver.com</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
@@ -6538,7 +6770,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6785,11 @@
           <t>꽃잎사이다</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>movie6miri@naver.com</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
@@ -6628,7 +6864,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6958,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6973,11 @@
           <t>아이원헤어</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>leeareum96@naver.com</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
@@ -6812,7 +7052,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6827,7 +7067,11 @@
           <t>더끌림헤어</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>kklim7512820@naver.com</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
@@ -6898,7 +7142,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6913,7 +7157,11 @@
           <t>젠틀맨</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>dannykim2010@naver.com</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
@@ -6988,7 +7236,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7251,11 @@
           <t>서흥이발관</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>humble6551@naver.com</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
@@ -7074,7 +7326,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7089,7 +7341,11 @@
           <t>현대이발관</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>sacheoncity@naver.com</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
@@ -7160,7 +7416,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7175,7 +7431,11 @@
           <t>시대이발관</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ic-museum@naver.com</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
@@ -7250,7 +7510,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_hair/동구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/동구_미용실.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>duswls1338@naver.com</t>
+          <t>red8276@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -2713,7 +2713,11 @@
           <t>살롱드비아</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>tpfud1124@naver.com</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
@@ -3547,7 +3551,11 @@
           <t>한지수헤어스타</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>love444477@naver.com</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
@@ -3733,7 +3741,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ouou1771@naver.com</t>
+          <t>korea20027@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -4193,7 +4201,11 @@
           <t>은지헤어샵</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>south0429@naver.com</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
@@ -5673,7 +5685,11 @@
           <t>다온헤어</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>gjraby00@naver.com</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
@@ -6135,7 +6151,11 @@
           <t>아델라 헤어</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>hkhj8083@naver.com</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
@@ -6225,7 +6245,11 @@
           <t>머리만들기</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>greencoy79@naver.com</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_hair/동구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/동구_미용실.xlsx
@@ -567,11 +567,7 @@
           <t>블루가이</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>red8276@naver.com</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
@@ -1687,11 +1683,7 @@
           <t>긋시아헤어 동인천역 본점</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>lovedarl2@naver.com</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
@@ -1875,11 +1867,7 @@
           <t>요미살롱</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>minji_3-@naver.com</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
@@ -1969,11 +1957,7 @@
           <t>블루마린미용실</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>hairyuep@naver.com</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
@@ -2251,11 +2235,7 @@
           <t>카리스마</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>jackieyou@naver.com</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
@@ -2529,11 +2509,7 @@
           <t>에스제이헤어</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>emkim1003@naver.com</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
@@ -2619,11 +2595,7 @@
           <t>어나더스타일</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>jadenchoe@naver.com</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
@@ -3081,11 +3053,7 @@
           <t>양지헤어모디컬 송림1호점</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>justdoit0706@naver.com</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
@@ -3269,11 +3237,7 @@
           <t>솔빛헤어샾</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>lovesmoothz@naver.com</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
@@ -3457,11 +3421,7 @@
           <t>김영선헤어파라팜</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>hjstylemm@naver.com</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
@@ -3739,11 +3699,7 @@
           <t>퀸헤어</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>korea20027@naver.com</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
@@ -3829,11 +3785,7 @@
           <t>아가페헤어모드</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>hiksanin@naver.com</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
@@ -3923,11 +3875,7 @@
           <t>젠틀맨</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>dannykim2010@naver.com</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
@@ -4851,11 +4799,7 @@
           <t>모퉁이미장원</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>nijal99@naver.com</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
@@ -6527,11 +6471,7 @@
           <t>남자만들기</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>timmy0326@naver.com</t>
-        </is>
-      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
@@ -6621,11 +6561,7 @@
           <t>임진선헤어모드</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>hjstylemm@naver.com</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
@@ -7091,11 +7027,7 @@
           <t>더끌림헤어</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>kklim7512820@naver.com</t>
-        </is>
-      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
@@ -7181,11 +7113,7 @@
           <t>젠틀맨</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>dannykim2010@naver.com</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
@@ -7365,11 +7293,7 @@
           <t>현대이발관</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>sacheoncity@naver.com</t>
-        </is>
-      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>

--- a/naver-place-crawler/results_hair/동구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/동구_미용실.xlsx
@@ -567,7 +567,11 @@
           <t>블루가이</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lymm1272@naver.com</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
@@ -748,24 +752,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>헤어블리스</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>mini2028@naver.com</t>
-        </is>
-      </c>
+          <t>그린헤어샵</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1405-3910</t>
+          <t>032-764-3889</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 동구 솔빛로 21 솔빛마을아파트상가C동 101호 헤어블리스</t>
+          <t>인천광역시 동구 연송로 7</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="Q4" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,12 +820,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>125460993</t>
+          <t>1759485173</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/125460993</t>
+          <t>https://m.place.naver.com/place/1759485173</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -842,24 +842,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>그린헤어샵</t>
+          <t>웨이비헤어</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>yjd4843@naver.com</t>
+          <t>banana2728@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>032-764-3889</t>
+          <t>032-765-6500</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 동구 연송로 7</t>
+          <t>인천광역시 동구 화수로 8-8 웨이비헤어</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,12 +914,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1759485173</t>
+          <t>1547742205</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759485173</t>
+          <t>https://m.place.naver.com/place/1547742205</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -936,24 +936,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>웨이비헤어</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>banana2728@naver.com</t>
-        </is>
-      </c>
+          <t>찌꼬뽀꼬</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>032-765-6500</t>
+          <t>0507-1372-6177</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수로 8-8 웨이비헤어</t>
+          <t>인천광역시 동구 화수로 70</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -993,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +1004,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1547742205</t>
+          <t>19403616</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1547742205</t>
+          <t>https://m.place.naver.com/place/19403616</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1030,24 +1026,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>찌꼬뽀꼬</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ggiccoppocco@naver.com</t>
-        </is>
-      </c>
+          <t>신데렐라헤어살롱</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1372-6177</t>
+          <t>032-205-2006</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수로 70</t>
+          <t>인천광역시 동구 송현로 18 찬린빌딩 1층 신데렐라헤어살롱</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1087,13 +1079,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,12 +1094,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>19403616</t>
+          <t>1895187501</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19403616</t>
+          <t>https://m.place.naver.com/place/1895187501</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1124,29 +1116,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>신데렐라헤어살롱</t>
+          <t>다가즈 헤어 동인천점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>wonjung8542@naver.com</t>
+          <t>tmxkdlf70@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>032-205-2006</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 18 찬린빌딩 1층 신데렐라헤어살롱</t>
+          <t>인천광역시 동구 금곡로 7 1층 일부</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://다가즈헤어</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1156,7 +1144,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1181,13 +1169,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>32</v>
+        <v>231</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>33</v>
+        <v>235</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,12 +1184,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1895187501</t>
+          <t>1407309471</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895187501</t>
+          <t>https://m.place.naver.com/place/1407309471</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1218,12 +1206,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>다가즈 헤어 동인천점</t>
+          <t>문헤어</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tmxkdlf70@naver.com</t>
+          <t>moonhair2024@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1231,12 +1219,12 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 동구 금곡로 7 1층 일부</t>
+          <t>인천광역시 동구 샛골로161번길 23</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://다가즈헤어</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1246,7 +1234,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1271,13 +1259,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>231</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>235</v>
+        <v>2</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,12 +1274,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1407309471</t>
+          <t>1855219075</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1407309471</t>
+          <t>https://m.place.naver.com/place/1855219075</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1402,20 +1390,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>고은헤어</t>
+          <t>송이미용실</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>goodkej104@naver.com</t>
+          <t>alohasy0792@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>032-777-9981</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로 123</t>
+          <t>인천광역시 동구 금곡로 46-1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1455,13 +1447,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1470,12 +1462,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2140142713</t>
+          <t>1134477950</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2140142713</t>
+          <t>https://m.place.naver.com/place/1134477950</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1613,7 +1605,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1623,7 +1615,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1683,7 +1675,11 @@
           <t>긋시아헤어 동인천역 본점</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>lovedarl2@naver.com</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
@@ -2049,7 +2045,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dojin440@naver.com</t>
+          <t>do_hair2021@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2138,24 +2134,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>송이미용실</t>
+          <t>고은헤어</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>alohasy0792@naver.com</t>
+          <t>goodkej104@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>032-777-9981</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 동구 금곡로 46-1</t>
+          <t>인천광역시 동구 샛골로 123</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2195,13 +2187,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2210,12 +2202,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1134477950</t>
+          <t>2140142713</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134477950</t>
+          <t>https://m.place.naver.com/place/2140142713</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2235,7 +2227,11 @@
           <t>카리스마</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jackieyou@naver.com</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
@@ -2509,7 +2505,11 @@
           <t>에스제이헤어</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>emkim1003@naver.com</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
@@ -3053,7 +3053,11 @@
           <t>양지헤어모디컬 송림1호점</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>justdoit0706@naver.com</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
@@ -3143,11 +3147,7 @@
           <t>조이헤어샵</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>wedbl@naver.com</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
@@ -3237,7 +3237,11 @@
           <t>솔빛헤어샾</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>lovesmoothz@naver.com</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
@@ -3421,7 +3425,11 @@
           <t>김영선헤어파라팜</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>hjstylemm@naver.com</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
@@ -3785,7 +3793,11 @@
           <t>아가페헤어모드</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>hiksanin@naver.com</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
@@ -3875,7 +3887,11 @@
           <t>젠틀맨</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>dannykim2010@naver.com</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
@@ -3965,11 +3981,7 @@
           <t>루나헤어</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>hott0116@naver.com</t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
@@ -4055,11 +4067,7 @@
           <t>앨리스헤어</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>oh-hair@naver.com</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
@@ -4243,11 +4251,7 @@
           <t>헤어5.5</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>tnrua34@naver.com</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
@@ -4337,11 +4341,7 @@
           <t>칼라헤어샵</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>color63676@naver.com</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
@@ -4615,11 +4615,7 @@
           <t>그녀는예뻤다헤어샵</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>curablee@naver.com</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
@@ -4799,7 +4795,11 @@
           <t>모퉁이미장원</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>nijal99@naver.com</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>gashwoon@naver.com</t>
+          <t>hwani-0627@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -5719,11 +5719,7 @@
           <t>착한미용실</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>slayfox@naver.com</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
@@ -5907,11 +5903,7 @@
           <t>헤어박스</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>kpackage@naver.com</t>
-        </is>
-      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
@@ -6001,11 +5993,7 @@
           <t>초이스헤어</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>nrzzzzzz@naver.com</t>
-        </is>
-      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
@@ -6095,11 +6083,7 @@
           <t>아델라 헤어</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>hkhj8083@naver.com</t>
-        </is>
-      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
@@ -6189,11 +6173,7 @@
           <t>머리만들기</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>greencoy79@naver.com</t>
-        </is>
-      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
@@ -6377,11 +6357,7 @@
           <t>미카엘헤어</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>lhw2611@naver.com</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
@@ -6561,7 +6537,11 @@
           <t>임진선헤어모드</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>hjstylemm@naver.com</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
@@ -6705,13 +6685,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -7027,7 +7007,11 @@
           <t>더끌림헤어</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>kklim7512820@naver.com</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
@@ -7293,7 +7277,11 @@
           <t>현대이발관</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>sacheoncity@naver.com</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
@@ -7379,11 +7367,7 @@
           <t>시대이발관</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>ic-museum@naver.com</t>
-        </is>
-      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_hair/동구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/동구_미용실.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,29 +559,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>남성전문미용실</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>블루가이</t>
+          <t>퀸헤어</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lymm1272@naver.com</t>
+          <t>korea20027@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1387-2636</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수로 7 105호 블루가이</t>
+          <t>인천광역시 동구 솔빛로 9-1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -621,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1166035314</t>
+          <t>1978295708</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166035314</t>
+          <t>https://m.place.naver.com/place/1978295708</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -658,24 +654,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>헤어코코</t>
+          <t>루나헤어</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>n_n_v_v@naver.com</t>
+          <t>hott0116@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>032-777-3756</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로 182</t>
+          <t>인천광역시 동구 송향로 25 송림휴먼시아1단지상가 2층 루나헤어</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -715,13 +707,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +722,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>38368788</t>
+          <t>1171302617</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38368788</t>
+          <t>https://m.place.naver.com/place/1171302617</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -752,20 +744,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>그린헤어샵</t>
+          <t>문은혜프로헤어</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>032-764-3889</t>
+          <t>032-763-3749</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 동구 연송로 7</t>
+          <t>인천광역시 동구 송현로59번길 2-6</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -805,13 +797,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +812,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1759485173</t>
+          <t>19404459</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759485173</t>
+          <t>https://m.place.naver.com/place/19404459</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -842,24 +834,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>웨이비헤어</t>
+          <t>금빛미용실</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>banana2728@naver.com</t>
+          <t>surjunmam@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>032-765-6500</t>
+          <t>032-765-9844</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수로 8-8 웨이비헤어</t>
+          <t>인천광역시 동구 송현로 49</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,13 +891,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +906,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1547742205</t>
+          <t>15002935</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1547742205</t>
+          <t>https://m.place.naver.com/place/15002935</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -936,20 +928,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>찌꼬뽀꼬</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>레지나헤어</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>zipyzigi2001@naver.com</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1372-6177</t>
+          <t>0507-1363-7202</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수로 70</t>
+          <t>인천광역시 동구 송현로 25 2층 208호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -989,13 +985,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,17 +1000,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>19403616</t>
+          <t>1470301527</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19403616</t>
+          <t>https://m.place.naver.com/place/1470301527</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -1026,20 +1022,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>신데렐라헤어살롱</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>챠밍헤어클럽</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ls_42@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>032-205-2006</t>
+          <t>032-773-0388</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 18 찬린빌딩 1층 신데렐라헤어살롱</t>
+          <t>인천광역시 동구 화도진로 4 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1094,17 +1094,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1895187501</t>
+          <t>21462837</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895187501</t>
+          <t>https://m.place.naver.com/place/21462837</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -1116,25 +1116,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>다가즈 헤어 동인천점</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>tmxkdlf70@naver.com</t>
-        </is>
-      </c>
+          <t>아이원헤어</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>032-766-0057</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 동구 금곡로 7 1층 일부</t>
+          <t>인천광역시 동구 송미로 6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://다가즈헤어</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>231</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>235</v>
+        <v>41</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1407309471</t>
+          <t>1479009176</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1407309471</t>
+          <t>https://m.place.naver.com/place/1479009176</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>문헤어</t>
+          <t>남성여성커트전문점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>moonhair2024@naver.com</t>
+          <t>rose2334@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1219,7 +1219,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로161번길 23</t>
+          <t>인천광역시 동구 샛골로161번길 26 (송림동) 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1259,13 +1259,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1274,17 +1274,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1855219075</t>
+          <t>1002831879</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1855219075</t>
+          <t>https://m.place.naver.com/place/1002831879</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -1296,24 +1296,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>그린미용실</t>
+          <t>살롱드비아</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>govl733@naver.com</t>
+          <t>tpfud1124@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>032-763-1355</t>
+          <t>032-766-4296</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로109번길 48</t>
+          <t>인천광역시 동구 송림로 119</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1368,17 +1368,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>38355684</t>
+          <t>30858394</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38355684</t>
+          <t>https://m.place.naver.com/place/30858394</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -1390,24 +1390,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>송이미용실</t>
+          <t>조이헤어샵</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>alohasy0792@naver.com</t>
+          <t>wedbl@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>032-777-9981</t>
+          <t>032-761-7422</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 동구 금곡로 46-1</t>
+          <t>인천광역시 동구 송림로 100 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1447,13 +1447,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1134477950</t>
+          <t>34098453</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134477950</t>
+          <t>https://m.place.naver.com/place/34098453</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -1484,24 +1484,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>오르세헤어</t>
+          <t>헤어박스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dhgngkstlek@naver.com</t>
+          <t>kpackage@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1449-3478</t>
+          <t>032-777-0629</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로162번길 10 B1층 B106호</t>
+          <t>인천광역시 동구 송현로 44 A동 1층 107호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1556,17 +1556,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1467598688</t>
+          <t>37392373</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1467598688</t>
+          <t>https://m.place.naver.com/place/37392373</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -1578,44 +1578,44 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>헤어 림</t>
+          <t>요미살롱</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>amurug1_nuna@naver.com</t>
+          <t>minji_3-@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1313-3759</t>
+          <t>032-713-5020</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 동구 금곡로 62 1층</t>
+          <t>인천광역시 동구 송화로 4-1 1층 요미살롱Yomi Salon</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hair_lim_22</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>170</v>
+        <v>36</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>171</v>
+        <v>36</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1650,17 +1650,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1283134246</t>
+          <t>1962904477</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1283134246</t>
+          <t>https://m.place.naver.com/place/1962904477</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -1672,29 +1672,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>긋시아헤어 동인천역 본점</t>
+          <t>다가즈 헤어 동인천점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lovedarl2@naver.com</t>
+          <t>tmxkdlf70@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1381-4590</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 동구 솔빛로 11 2층</t>
+          <t>인천광역시 동구 금곡로 7 1층 일부</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://다가즈헤어</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1704,7 +1700,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1729,13 +1725,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>288</v>
+        <v>233</v>
       </c>
       <c r="Q14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>295</v>
+        <v>237</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1744,17 +1740,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>16377388</t>
+          <t>1407309471</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16377388</t>
+          <t>https://m.place.naver.com/place/1407309471</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -1766,29 +1762,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>감성헤어 인천도원점</t>
+          <t>헤어블리스</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>khy9747@naver.com</t>
+          <t>mini2028@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1359-2542</t>
+          <t>0507-1405-3910</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로 101-1 감성헤어 인천도원점</t>
+          <t>인천광역시 동구 솔빛로 21 솔빛마을아파트상가C동 101호 헤어블리스</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/khy9747</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1798,12 +1794,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1823,13 +1819,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="R15" t="n">
-        <v>163</v>
+        <v>102</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1838,17 +1834,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>36540826</t>
+          <t>125460993</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36540826</t>
+          <t>https://m.place.naver.com/place/125460993</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -1860,20 +1856,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>요미살롱</t>
+          <t>지나샵헤어</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>032-713-5020</t>
+          <t>0507-1358-0189</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송화로 4-1 1층 요미살롱Yomi Salon</t>
+          <t>인천광역시 동구 송현로 44 솔빛마을 상가A동 204호 지나샵헤어</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1913,13 +1909,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1928,17 +1924,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1962904477</t>
+          <t>1163396883</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1962904477</t>
+          <t>https://m.place.naver.com/place/1163396883</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -1950,25 +1946,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>블루마린미용실</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>이슈헤어</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>issuse_4905@naver.com</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>032-761-2409</t>
+          <t>0507-1362-1884</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 동구 우각로 36 1층</t>
+          <t>인천광역시 동구 샛골로194번길 20 이슈헤어</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/issuse_4905</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1999,17 +1999,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="R17" t="n">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2018,17 +2018,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2057984078</t>
+          <t>1699619730</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2057984078</t>
+          <t>https://m.place.naver.com/place/1699619730</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -2040,24 +2040,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>디오헤어</t>
+          <t>긋시아헤어 동인천역 본점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>do_hair2021@naver.com</t>
+          <t>lovedarl2@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1407-0424</t>
+          <t>0507-1381-4590</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로 109 화도진그린빌아파트상가104호</t>
+          <t>인천광역시 동구 솔빛로 11 2층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2097,13 +2097,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>15</v>
+        <v>289</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R18" t="n">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2112,17 +2112,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>36721103</t>
+          <t>16377388</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36721103</t>
+          <t>https://m.place.naver.com/place/16377388</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -2134,20 +2134,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>고은헤어</t>
+          <t>헤어코코</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>goodkej104@naver.com</t>
+          <t>meowdeling@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>032-777-3756</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로 123</t>
+          <t>인천광역시 동구 화도진로 182</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2187,13 +2191,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2202,17 +2206,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2140142713</t>
+          <t>38368788</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2140142713</t>
+          <t>https://m.place.naver.com/place/38368788</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -2224,24 +2228,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>카리스마</t>
+          <t>블루마린미용실</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jackieyou@naver.com</t>
+          <t>hairyuep@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1344-7962</t>
+          <t>032-761-2409</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수로 9 1층</t>
+          <t>인천광역시 동구 우각로 36 1층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2281,13 +2285,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2296,17 +2300,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2009179994</t>
+          <t>2057984078</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009179994</t>
+          <t>https://m.place.naver.com/place/2057984078</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -2318,24 +2322,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>나타나엘헤어</t>
+          <t>김민경헤어살롱</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>yuujiin@naver.com</t>
+          <t>r8414250@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1366-8670</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로184번길 8 1층</t>
+          <t>인천광역시 동구 화도진로 38-2</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2390,17 +2390,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1948114724</t>
+          <t>1610875246</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1948114724</t>
+          <t>https://m.place.naver.com/place/1610875246</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -2412,25 +2412,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>준헤어아트</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>jie0105@naver.com</t>
-        </is>
-      </c>
+          <t>올뎃헤어</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>032-777-8680</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 동구 제물량로 403-1 1층 101호</t>
+          <t>인천광역시 동구 송현로 24 솔빛마을 상가B동</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jun_hairart/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2461,17 +2461,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2480,17 +2480,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1124957403</t>
+          <t>1573772013</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1124957403</t>
+          <t>https://m.place.naver.com/place/1573772013</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -2502,20 +2502,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>에스제이헤어</t>
+          <t>머리만들기</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>emkim1003@naver.com</t>
+          <t>greencoy79@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>032-761-6993</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로95번길 14</t>
+          <t>인천광역시 동구 송림로 114 1층 머리만들기미용실</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2555,13 +2559,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2570,17 +2574,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1214956821</t>
+          <t>21495793</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1214956821</t>
+          <t>https://m.place.naver.com/place/21495793</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -2592,20 +2596,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>어나더스타일</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>임진선헤어모드</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>hjstylemm@naver.com</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1404-0634</t>
+          <t>032-766-5867</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 16 101호</t>
+          <t>인천광역시 동구 화도진로 109 107호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2645,13 +2653,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="Q24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>160</v>
+        <v>4</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2660,17 +2668,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1200032840</t>
+          <t>1295033502</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1200032840</t>
+          <t>https://m.place.naver.com/place/1295033502</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -2682,24 +2690,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>살롱드비아</t>
+          <t>어나더스타일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>tpfud1124@naver.com</t>
+          <t>jadenchoe@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>032-766-4296</t>
+          <t>0507-1404-0634</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 119</t>
+          <t>인천광역시 동구 송림로 16 101호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2739,13 +2747,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R25" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2754,47 +2762,51 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>30858394</t>
+          <t>1200032840</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/30858394</t>
+          <t>https://m.place.naver.com/place/1200032840</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>정아미용실</t>
+          <t>남자만들기</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bora4141@naver.com</t>
+          <t>ghgh3036@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1498-0254</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송화로39번길 6-3</t>
+          <t>인천광역시 동구 새천년로 35 1층 남자만들기</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/made_._man?igsh=Mzh0anI5djBpenJp</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2804,7 +2816,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2825,17 +2837,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2844,17 +2856,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1546870027</t>
+          <t>1095533065</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1546870027</t>
+          <t>https://m.place.naver.com/place/1095533065</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -2866,20 +2878,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>태쁘헤어</t>
+          <t>신데렐라헤어살롱</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>tjdwlsl2004@naver.com</t>
+          <t>wonjung8542@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>032-205-2006</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 동구 제물량로 405</t>
+          <t>인천광역시 동구 송현로 18 찬린빌딩 1층 신데렐라헤어살롱</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2919,13 +2935,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2934,17 +2950,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1775472017</t>
+          <t>1895187501</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1775472017</t>
+          <t>https://m.place.naver.com/place/1895187501</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -2956,24 +2972,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>보헤미안헤어</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>125_suu@naver.com</t>
-        </is>
-      </c>
+          <t>엘림헤어샵</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>032-765-6565</t>
+          <t>032-761-2504</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 13-1</t>
+          <t>인천광역시 동구 송현로 37</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3013,13 +3025,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3028,17 +3040,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>21478300</t>
+          <t>20385139</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21478300</t>
+          <t>https://m.place.naver.com/place/20385139</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -3050,24 +3062,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>양지헤어모디컬 송림1호점</t>
+          <t>김영선헤어파라팜</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>justdoit0706@naver.com</t>
+          <t>hjstylemm@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>032-773-6603</t>
+          <t>032-762-9122</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 동구 금곡로82번길 1</t>
+          <t>인천광역시 동구 송화로 9</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3107,13 +3119,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3122,42 +3134,46 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>19404423</t>
+          <t>19395909</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19404423</t>
+          <t>https://m.place.naver.com/place/19395909</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>조이헤어샵</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>젠틀맨</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>dannykim2010@naver.com</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>032-761-7422</t>
+          <t>032-243-1630</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 100 2층</t>
+          <t>인천광역시 동구 송현로 35 1층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3197,13 +3213,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3212,17 +3228,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>34098453</t>
+          <t>1431074793</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34098453</t>
+          <t>https://m.place.naver.com/place/1431074793</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -3234,24 +3250,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>솔빛헤어샾</t>
+          <t>그녀는예뻤다헤어샵</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>lovesmoothz@naver.com</t>
+          <t>rmsusms403@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>032-761-7449</t>
+          <t>032-773-3752</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 50 솔빛마을주공아파트</t>
+          <t>인천광역시 동구 송림로 77-2</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3291,13 +3307,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3306,17 +3322,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1909849664</t>
+          <t>21488158</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1909849664</t>
+          <t>https://m.place.naver.com/place/21488158</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -3328,29 +3344,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>이슈헤어</t>
+          <t>찌꼬뽀꼬</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>issuse_4905@naver.com</t>
+          <t>skdi3277@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1362-1884</t>
+          <t>0507-1372-6177</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로194번길 20 이슈헤어</t>
+          <t>인천광역시 동구 화수로 70</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/issuse_4905</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3360,12 +3376,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3381,17 +3397,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="Q32" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3400,17 +3416,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1699619730</t>
+          <t>19403616</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699619730</t>
+          <t>https://m.place.naver.com/place/19403616</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -3422,29 +3438,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>김영선헤어파라팜</t>
+          <t>휴이엠헤어 인천송현점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>hjstylemm@naver.com</t>
+          <t>nicerola@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>032-762-9122</t>
+          <t>0507-1356-0402</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송화로 9</t>
+          <t>인천광역시 동구 송현로 47 3층 휴이엠헤어</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nicerola</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3454,12 +3470,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3475,17 +3491,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>84</v>
+        <v>5319</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="R33" t="n">
-        <v>84</v>
+        <v>5378</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3494,17 +3510,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>19395909</t>
+          <t>1258677936</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19395909</t>
+          <t>https://m.place.naver.com/place/1258677936</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -3516,24 +3532,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>한지수헤어스타</t>
+          <t>다온헤어</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>love444477@naver.com</t>
+          <t>hyuni0322@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>032-773-2022</t>
+          <t>032-762-6401</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 41-3</t>
+          <t>인천광역시 동구 송현로 24 솔빛마을 상가B동</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3573,13 +3589,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>155</v>
+        <v>27</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>155</v>
+        <v>27</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3588,17 +3604,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>19399892</t>
+          <t>21504919</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19399892</t>
+          <t>https://m.place.naver.com/place/21504919</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -3610,24 +3626,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>달컴헤어</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>moonsb1206@naver.com</t>
-        </is>
-      </c>
+          <t>에스제이헤어</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0507-1411-0574</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로 16 상가동 2층 202호</t>
+          <t>인천광역시 동구 화도진로95번길 14</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3667,13 +3675,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>374</v>
+        <v>23</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>376</v>
+        <v>24</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3682,17 +3690,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2086610462</t>
+          <t>1214956821</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2086610462</t>
+          <t>https://m.place.naver.com/place/1214956821</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -3704,16 +3712,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>퀸헤어</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>예쁜머리</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>dailysenti@naver.com</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 동구 솔빛로 9-1</t>
+          <t>인천광역시 동구 새천년로38번길 11</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3753,13 +3765,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3768,17 +3780,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1978295708</t>
+          <t>1919480231</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1978295708</t>
+          <t>https://m.place.naver.com/place/1919480231</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -3790,24 +3802,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>아가페헤어모드</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>hiksanin@naver.com</t>
-        </is>
-      </c>
+          <t>달컴헤어</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>032-777-8907</t>
+          <t>0507-1411-0574</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로 183 만석비치타운 상가</t>
+          <t>인천광역시 동구 화도진로 16 상가동 2층 202호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3847,13 +3855,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>58</v>
+        <v>381</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>58</v>
+        <v>383</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3862,46 +3870,38 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>16374330</t>
+          <t>2086610462</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16374330</t>
+          <t>https://m.place.naver.com/place/2086610462</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>남성전문미용실</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>젠틀맨</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>dannykim2010@naver.com</t>
-        </is>
-      </c>
+          <t>태쁘헤어</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>032-243-1630</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 35 1층</t>
+          <t>인천광역시 동구 제물량로 405</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3941,13 +3941,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3956,17 +3956,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1431074793</t>
+          <t>1775472017</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1431074793</t>
+          <t>https://m.place.naver.com/place/1775472017</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -3978,16 +3978,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>루나헤어</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>명동미용실</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>cicipo22@naver.com</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>032-762-5484</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송향로 25 송림휴먼시아1단지상가 2층 루나헤어</t>
+          <t>인천광역시 동구 석수로 31</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4027,13 +4035,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4042,17 +4050,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1171302617</t>
+          <t>21488806</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1171302617</t>
+          <t>https://m.place.naver.com/place/21488806</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -4064,20 +4072,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>앨리스헤어</t>
+          <t>착한미용실</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0507-1304-1237</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수로 7 엘리스헤어</t>
+          <t>인천광역시 동구 샛골로161번길 32</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4117,14 +4121,14 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" t="n">
-        <v>40</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>X</t>
@@ -4132,17 +4136,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1884271441</t>
+          <t>1508453933</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1884271441</t>
+          <t>https://m.place.naver.com/place/1508453933</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -4154,24 +4158,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>은지헤어샵</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>south0429@naver.com</t>
-        </is>
-      </c>
+          <t>칼라헤어샵</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>032-766-5651</t>
+          <t>032-777-6719</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도로33번길 1</t>
+          <t>인천광역시 동구 인중로680번길 16</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4211,13 +4211,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4226,17 +4226,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>15003018</t>
+          <t>21504340</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/15003018</t>
+          <t>https://m.place.naver.com/place/21504340</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -4248,20 +4248,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>헤어5.5</t>
+          <t>그린헤어샵</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1498-8336</t>
+          <t>032-764-3889</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 24 101호</t>
+          <t>인천광역시 동구 연송로 7</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4301,13 +4301,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4316,17 +4316,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1004265686</t>
+          <t>1759485173</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1004265686</t>
+          <t>https://m.place.naver.com/place/1759485173</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -4338,20 +4338,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>칼라헤어샵</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>모퉁이미장원</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>nijal99@naver.com</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>032-777-6719</t>
+          <t>0507-1418-1608</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 동구 인중로680번길 16</t>
+          <t>인천광역시 동구 샛골로 184 1층 모퉁이미장원</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4391,13 +4395,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4406,17 +4410,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>21504340</t>
+          <t>38358873</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21504340</t>
+          <t>https://m.place.naver.com/place/38358873</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -4428,24 +4432,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>오늘은머리하는날</t>
+          <t>은지헤어샵</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>uiryeonginfo@naver.com</t>
+          <t>south0429@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>032-761-2772</t>
+          <t>032-766-5651</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 동구 석수로 10</t>
+          <t>인천광역시 동구 화도로33번길 1</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4485,13 +4489,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4500,17 +4504,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>38365923</t>
+          <t>15003018</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38365923</t>
+          <t>https://m.place.naver.com/place/15003018</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -4522,20 +4526,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>예쁜머리</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>propshop@naver.com</t>
-        </is>
-      </c>
+          <t>끌레헤어</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1376-2621</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 동구 새천년로38번길 11</t>
+          <t>인천광역시 동구 샛골로 200 끌레헤어</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4575,13 +4579,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4590,17 +4594,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1919480231</t>
+          <t>32027200</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1919480231</t>
+          <t>https://m.place.naver.com/place/32027200</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -4612,25 +4616,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>그녀는예뻤다헤어샵</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>감성헤어 인천도원점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>khy9747@naver.com</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>032-773-3752</t>
+          <t>0507-1359-2542</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 77-2</t>
+          <t>인천광역시 동구 샛골로 101-1 감성헤어 인천도원점</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/khy9747</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4640,12 +4648,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4665,13 +4673,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="R46" t="n">
-        <v>10</v>
+        <v>165</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4680,17 +4688,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>21488158</t>
+          <t>36540826</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21488158</t>
+          <t>https://m.place.naver.com/place/36540826</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -4702,20 +4710,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>장헤어샵</t>
+          <t>블루가이</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jjongs10@naver.com</t>
+          <t>lymm1272@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1387-2636</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 38</t>
+          <t>인천광역시 동구 화수로 7 105호 블루가이</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4755,13 +4767,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4770,17 +4782,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1241940292</t>
+          <t>1166035314</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1241940292</t>
+          <t>https://m.place.naver.com/place/1166035314</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -4792,29 +4804,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>모퉁이미장원</t>
+          <t>헤어 림</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>nijal99@naver.com</t>
+          <t>amurug1_nuna@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1418-1608</t>
+          <t>0507-1313-3759</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로 184 1층 모퉁이미장원</t>
+          <t>인천광역시 동구 금곡로 62 1층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/hair_lim_22</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4824,7 +4836,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4845,17 +4857,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>87</v>
+        <v>170</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>87</v>
+        <v>171</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4864,17 +4876,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>38358873</t>
+          <t>1283134246</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38358873</t>
+          <t>https://m.place.naver.com/place/1283134246</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -4886,20 +4898,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>N.5 송현점</t>
+          <t>진헤어</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>nabannnn@naver.com</t>
+          <t>sspmj501@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1360-3840</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 17 1층</t>
+          <t>인천광역시 동구 송현로 38 1층 103호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4939,13 +4955,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4954,17 +4970,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1678288450</t>
+          <t>1179064652</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1678288450</t>
+          <t>https://m.place.naver.com/place/1179064652</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -4976,24 +4992,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>챠밍헤어클럽</t>
+          <t>아델라 헤어</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>dongsimgi1004@naver.com</t>
+          <t>hkhj8083@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>032-773-0388</t>
+          <t>0507-1375-2616</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로 4 1층</t>
+          <t>인천광역시 동구 송림로162번길 10 116호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5033,13 +5049,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>58</v>
+        <v>417</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>59</v>
+        <v>418</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5048,17 +5064,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>21462837</t>
+          <t>1100717476</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21462837</t>
+          <t>https://m.place.naver.com/place/1100717476</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -5070,24 +5086,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>올뎃헤어</t>
+          <t>N.5 송현점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>hwani-0627@naver.com</t>
+          <t>nabannnn@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>032-777-8680</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 24 솔빛마을 상가B동</t>
+          <t>인천광역시 동구 송현로 17 1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5127,13 +5139,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5142,17 +5154,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1573772013</t>
+          <t>1678288450</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1573772013</t>
+          <t>https://m.place.naver.com/place/1678288450</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -5164,24 +5176,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>유나샵</t>
+          <t>나타나엘헤어</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>yuna10110@naver.com</t>
+          <t>yuujiin@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1329-8747</t>
+          <t>0507-1366-8670</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 53-1 1층</t>
+          <t>인천광역시 동구 샛골로184번길 8 1층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5221,13 +5233,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5236,17 +5248,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1903346096</t>
+          <t>1948114724</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1903346096</t>
+          <t>https://m.place.naver.com/place/1948114724</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -5258,24 +5270,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>은헤어샵</t>
+          <t>고은헤어</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>dla_dp_fls@naver.com</t>
+          <t>goodkej104@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0507-1329-6081</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 동구 어촌로 22-6 B동101호</t>
+          <t>인천광역시 동구 샛골로 123</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5315,13 +5323,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5330,17 +5338,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1215333402</t>
+          <t>2140142713</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1215333402</t>
+          <t>https://m.place.naver.com/place/2140142713</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -5352,24 +5360,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>장미미용실</t>
+          <t>정아미용실</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>shanyingstar@naver.com</t>
+          <t>bora4141@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>032-773-2785</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로44번길 19</t>
+          <t>인천광역시 동구 송화로39번길 6-3</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5409,13 +5413,13 @@
         </is>
       </c>
       <c r="P54" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>1</v>
-      </c>
       <c r="R54" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5424,17 +5428,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1515226016</t>
+          <t>1546870027</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1515226016</t>
+          <t>https://m.place.naver.com/place/1546870027</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -5446,20 +5450,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>홈헤어살롱</t>
+          <t>은헤어샵</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jiyea_junjin@naver.com</t>
+          <t>dla_dp_fls@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1329-6081</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 동구 석수로 22 1층 13호</t>
+          <t>인천광역시 동구 어촌로 22-6 B동101호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5499,13 +5507,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="Q55" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5514,17 +5522,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1257624749</t>
+          <t>1215333402</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1257624749</t>
+          <t>https://m.place.naver.com/place/1215333402</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -5536,12 +5544,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>착한미용실</t>
+          <t>다온헤어</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>slayfox@naver.com</t>
+          <t>hyuni0322@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -5549,7 +5557,7 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로161번길 32</t>
+          <t>인천광역시 동구 운교로 6 1층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5589,13 +5597,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5604,17 +5612,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1508453933</t>
+          <t>1920018902</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1508453933</t>
+          <t>https://m.place.naver.com/place/1920018902</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -5626,20 +5634,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>다온헤어</t>
+          <t>헤어블루밍</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>gjraby00@naver.com</t>
+          <t>dayoung_1001@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>032-765-7885</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 동구 운교로 6 1층</t>
+          <t>인천광역시 동구 인중로 659</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5679,13 +5691,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5694,17 +5706,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1920018902</t>
+          <t>21486904</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1920018902</t>
+          <t>https://m.place.naver.com/place/21486904</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -5716,20 +5728,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>착한미용실</t>
+          <t>유나샵</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1338-1780</t>
+          <t>0507-1329-8747</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 동구 동산로 87-1</t>
+          <t>인천광역시 동구 송현로 53-1 1층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5769,13 +5781,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R58" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5784,17 +5796,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1494726931</t>
+          <t>1903346096</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1494726931</t>
+          <t>https://m.place.naver.com/place/1903346096</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -5806,29 +5818,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>휴이엠헤어 인천송현점</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>nicerola@naver.com</t>
-        </is>
-      </c>
+          <t>그린미용실</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1356-0402</t>
+          <t>032-763-1355</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 47 3층 휴이엠헤어</t>
+          <t>인천광역시 동구 송림로109번길 48</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nicerola</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5838,12 +5846,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5859,17 +5867,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>5294</v>
+        <v>78</v>
       </c>
       <c r="Q59" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>5353</v>
+        <v>78</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5878,17 +5886,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1258677936</t>
+          <t>38355684</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1258677936</t>
+          <t>https://m.place.naver.com/place/38355684</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -5900,20 +5908,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>헤어박스</t>
+          <t>송이미용실</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>032-777-0629</t>
+          <t>032-777-9981</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 44 A동 1층 107호</t>
+          <t>인천광역시 동구 금곡로 46-1</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5953,13 +5961,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -5968,17 +5976,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>37392373</t>
+          <t>1134477950</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37392373</t>
+          <t>https://m.place.naver.com/place/1134477950</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -5990,20 +5998,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>초이스헤어</t>
+          <t>헤어5.5</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1426-1095</t>
+          <t>0507-1498-8336</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수로 8-3 1층</t>
+          <t>인천광역시 동구 송현로 24 101호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6043,13 +6051,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R61" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6058,17 +6066,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>2097244334</t>
+          <t>1004265686</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2097244334</t>
+          <t>https://m.place.naver.com/place/1004265686</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -6080,20 +6088,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>아델라 헤어</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>오르세헤어</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>dhgngkstlek@naver.com</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1375-2616</t>
+          <t>0507-1449-3478</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로162번길 10 116호</t>
+          <t>인천광역시 동구 송림로162번길 10 B1층 B106호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6133,13 +6145,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>416</v>
+        <v>28</v>
       </c>
       <c r="Q62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R62" t="n">
-        <v>417</v>
+        <v>31</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6148,17 +6160,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1100717476</t>
+          <t>1467598688</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1100717476</t>
+          <t>https://m.place.naver.com/place/1467598688</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -6170,20 +6182,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>머리만들기</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>홈헤어살롱</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>jiyea_junjin@naver.com</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>032-761-6993</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 114 1층 머리만들기미용실</t>
+          <t>인천광역시 동구 석수로 22 1층 13호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6223,13 +6235,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R63" t="n">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6238,17 +6250,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>21495793</t>
+          <t>1257624749</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21495793</t>
+          <t>https://m.place.naver.com/place/1257624749</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -6260,24 +6272,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>레지나헤어</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>zipyzigi2001@naver.com</t>
-        </is>
-      </c>
+          <t>진선헤어샵</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1363-7202</t>
+          <t>032-763-0412</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 25 2층 208호</t>
+          <t>인천광역시 동구 금곡로103번길 17</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6317,13 +6325,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6332,17 +6340,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1470301527</t>
+          <t>38356443</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1470301527</t>
+          <t>https://m.place.naver.com/place/38356443</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -6354,20 +6362,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>미카엘헤어</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>꽃잎사이다</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>movie6miri@naver.com</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>032-764-3341</t>
+          <t>032-765-3535</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 43-2 미카엘헤어</t>
+          <t>인천광역시 동구 송현로 33 꽃잎사이다</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6407,13 +6419,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R65" t="n">
-        <v>44</v>
+        <v>229</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6422,47 +6434,51 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>38654675</t>
+          <t>350903194</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38654675</t>
+          <t>https://m.place.naver.com/place/350903194</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>남성전문미용실</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>남자만들기</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>한지수헤어스타</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>love444477@naver.com</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1498-0254</t>
+          <t>032-773-2022</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 동구 새천년로 35 1층 남자만들기</t>
+          <t>인천광역시 동구 송현로 41-3</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/made_._man?igsh=Mzh0anI5djBpenJp</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6472,7 +6488,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6493,17 +6509,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>31</v>
+        <v>155</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6512,17 +6528,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1095533065</t>
+          <t>19399892</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1095533065</t>
+          <t>https://m.place.naver.com/place/19399892</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -6534,24 +6550,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>임진선헤어모드</t>
+          <t>미카엘헤어</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>hjstylemm@naver.com</t>
+          <t>lhw2611@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>032-766-5867</t>
+          <t>032-764-3341</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로 109 107호</t>
+          <t>인천광역시 동구 송현로 43-2 미카엘헤어</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6591,13 +6607,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6606,46 +6622,46 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1295033502</t>
+          <t>38654675</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1295033502</t>
+          <t>https://m.place.naver.com/place/38654675</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>진헤어</t>
+          <t>젠틀맨</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>sspmj501@naver.com</t>
+          <t>dannykim2010@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1360-3840</t>
+          <t>032-777-4322</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 38 1층 103호</t>
+          <t>인천광역시 동구 송림로 82</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6685,13 +6701,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6700,17 +6716,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1179064652</t>
+          <t>1689383288</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1179064652</t>
+          <t>https://m.place.naver.com/place/1689383288</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -6722,24 +6738,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>꽃잎사이다</t>
+          <t>아가페헤어모드</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>movie6miri@naver.com</t>
+          <t>girl7029@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>032-765-3535</t>
+          <t>032-777-8907</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 33 꽃잎사이다</t>
+          <t>인천광역시 동구 화도진로 183 만석비치타운 상가</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6779,13 +6795,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>227</v>
+        <v>58</v>
       </c>
       <c r="Q69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>229</v>
+        <v>58</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6794,17 +6810,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>350903194</t>
+          <t>16374330</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/350903194</t>
+          <t>https://m.place.naver.com/place/16374330</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -6816,34 +6832,30 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>장소원헤어아트</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>nnyjjang@naver.com</t>
-        </is>
-      </c>
+          <t>카리스마</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>032-773-1113</t>
+          <t>0507-1344-7962</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 24 비상가 205호 큰도로 2층 아파트선 1층</t>
+          <t>인천광역시 동구 화수로 9 1층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>http://인천.지기.kr/tggccv</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6873,13 +6885,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>127</v>
+        <v>6</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>127</v>
+        <v>6</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6888,46 +6900,42 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>32696406</t>
+          <t>2009179994</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32696406</t>
+          <t>https://m.place.naver.com/place/2009179994</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>아이원헤어</t>
+          <t>현대이발관</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>leeareum96@naver.com</t>
+          <t>sacheoncity@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>032-766-0057</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송미로 6</t>
+          <t>인천광역시 동구 송림로110번길 5</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6967,13 +6975,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -6982,34 +6990,34 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1479009176</t>
+          <t>1412377982</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1479009176</t>
+          <t>https://m.place.naver.com/place/1412377982</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>더끌림헤어</t>
+          <t>삼각이용원</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>kklim7512820@naver.com</t>
+          <t>jjangting@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -7017,7 +7025,7 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송향로 25</t>
+          <t>인천광역시 동구 송화로 4-2</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7057,13 +7065,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7072,42 +7080,38 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1203938488</t>
+          <t>16380434</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1203938488</t>
+          <t>https://m.place.naver.com/place/16380434</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>남성전문미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>젠틀맨</t>
+          <t>새마을이용원</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>032-777-4322</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 82</t>
+          <t>인천광역시 동구 송림로70번길 19</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7147,13 +7151,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7162,17 +7166,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1689383288</t>
+          <t>1779313493</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1689383288</t>
+          <t>https://m.place.naver.com/place/1779313493</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -7184,20 +7188,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>서흥이발관</t>
+          <t>진흥이발관</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>humble6551@naver.com</t>
+          <t>aini_sy@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>032-772-8353</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림동 262</t>
+          <t>인천광역시 동구 샛골로 200</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7237,13 +7245,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7252,17 +7260,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>38353006</t>
+          <t>38351950</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38353006</t>
+          <t>https://m.place.naver.com/place/38351950</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -7274,20 +7282,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>현대이발관</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>sacheoncity@naver.com</t>
-        </is>
-      </c>
+          <t>서흥이발관</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로110번길 5</t>
+          <t>인천광역시 동구 송림동 262</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7327,13 +7331,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7342,17 +7346,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1412377982</t>
+          <t>38353006</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1412377982</t>
+          <t>https://m.place.naver.com/place/38353006</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7446,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
